--- a/SGC-CKN/Excel/582c8c77-664d-4e17-a211-f44f6df22123_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_p_7-116_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/582c8c77-664d-4e17-a211-f44f6df22123_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_p_7-116_D800_24-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-116</t>
+    <t>P7-46</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -92,7 +92,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -109,7 +109,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>5 Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">11:30
@@ -129,7 +129,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">14:10
@@ -139,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">14:40
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:20
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:50
@@ -169,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát sạn, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát sạn, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:10
@@ -182,9 +182,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">16:50
 24/03/2026</t>
   </si>
@@ -192,7 +189,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:55
@@ -1474,13 +1471,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="31">
         <v>-39.3</v>
@@ -1503,19 +1500,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>57</v>
       </c>
       <c r="F20" s="34">
         <v>-42.5</v>
@@ -1538,7 +1535,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1644,31 +1641,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1911,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1940,7 +1937,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1963,7 +1960,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>29</v>
